--- a/tc/업데이트_TC_2026-10_v1.xlsx
+++ b/tc/업데이트_TC_2026-10_v1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="128">
   <si>
     <t>No.</t>
   </si>
@@ -235,7 +235,7 @@
     <t xml:space="preserve">1. 각 업데이트 카드는 다음으로 구성됨
 - 버전 배지
 - 업데이트 제목
-- 게시 시작일
+- 배포일시(YYYY.MM.DD HH:MM)
 - 솔루션 배지(복수 가능)</t>
   </si>
   <si>
@@ -257,18 +257,18 @@
     <t>1. 카드에 솔루션 배지 노출(복수 솔루션은 해당 배지 모두 노출)</t>
   </si>
   <si>
-    <t>게시일</t>
-  </si>
-  <si>
-    <t>1. 카드 게시일 확인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 게시 시작일 노출 (YYYY.MM.DD)
-2. "등록:" 등 접두 라벨 없이 날짜만
-3. KST 기준(현재 국가별 환산 없이 KST 원본 + "KST" 라벨 임시)</t>
-  </si>
-  <si>
-    <t>미해결: 국가별 현지시간 환산 보류(ISSUE-079) - 기획 확인 필요</t>
+    <t>배포일시</t>
+  </si>
+  <si>
+    <t>1. 카드 배포일시 확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 배포일시 날짜+시:분 노출 (YYYY.MM.DD HH:MM)
+2. 한국어=라벨없음 / 그 외 언어=HH:MM KST
+3. "등록:" 등 접두 라벨 없음</t>
+  </si>
+  <si>
+    <t>2026-10-01 확정: "게시 시작일"→"배포일시", cs.html도 시:분 노출(formatUpdateDateTime). 국가별 환산은 보류(ISSUE-079). 홈 위젯은 날짜만(정적).</t>
   </si>
   <si>
     <t>정렬</t>
@@ -350,13 +350,17 @@
     <t>1. 업데이트 제목 노출</t>
   </si>
   <si>
-    <t>버전/게시일</t>
-  </si>
-  <si>
-    <t>1. 상세 버전·게시일 확인</t>
-  </si>
-  <si>
-    <t>1. 버전 배지 및 게시 시작일 노출(라벨 없이 날짜, KST)</t>
+    <t>버전/배포일시</t>
+  </si>
+  <si>
+    <t>1. 상세 버전·배포일시 확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 버전 배지 및 배포일시 노출 (YYYY.MM.DD HH:MM)
+2. 한국어=라벨없음 / 그 외 언어=HH:MM KST</t>
+  </si>
+  <si>
+    <t>2026-10-01: 목록·상세 모두 날짜+시:분.</t>
   </si>
   <si>
     <t>솔루션별 내용</t>
@@ -1715,7 +1719,7 @@
         <v>23</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -1726,7 +1730,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>26</v>
@@ -1735,10 +1739,10 @@
         <v>99</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>22</v>
@@ -1770,10 +1774,10 @@
         <v>99</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>22</v>
@@ -1796,19 +1800,19 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>22</v>
@@ -1831,7 +1835,7 @@
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>18</v>
@@ -1840,10 +1844,10 @@
         <v>99</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>22</v>
@@ -1865,22 +1869,22 @@
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>22</v>
@@ -1892,7 +1896,7 @@
         <v>23</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
